--- a/data/output/sim_gridrnd/REL1/group_520_40/results/REL1_G8_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL1/group_520_40/results/REL1_G8_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,384 +466,439 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S03_G8_521_42_REL1</t>
+          <t>S01_G8_521_40_REL1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>521</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D2" t="n">
-        <v>62.26834692364714</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
         <v>521</v>
@@ -852,228 +907,261 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>529.4339979406046</v>
-      </c>
-      <c r="J2" t="n">
-        <v>52.07923642321156</v>
-      </c>
-      <c r="K2" t="n">
-        <v>513.689788413475</v>
-      </c>
-      <c r="L2" t="n">
-        <v>48.39006515465952</v>
-      </c>
-      <c r="M2" t="n">
-        <v>515.3576681363147</v>
-      </c>
-      <c r="N2" t="n">
-        <v>54.89738191551174</v>
-      </c>
-      <c r="O2" t="n">
-        <v>521.8784837664444</v>
-      </c>
-      <c r="P2" t="n">
-        <v>57.36675926307823</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>525.1483841130859</v>
-      </c>
       <c r="R2" t="n">
-        <v>52.49041949888366</v>
+        <v>521.02</v>
       </c>
       <c r="S2" t="n">
-        <v>525.5726143669569</v>
+        <v>51.11</v>
       </c>
       <c r="T2" t="n">
-        <v>48.54232322386031</v>
+        <v>518.71</v>
       </c>
       <c r="U2" t="n">
-        <v>526.0044128103135</v>
+        <v>47.29</v>
       </c>
       <c r="V2" t="n">
-        <v>46.12099795151886</v>
+        <v>520.83</v>
       </c>
       <c r="W2" t="n">
-        <v>527.1527807777139</v>
+        <v>41.65</v>
       </c>
       <c r="X2" t="n">
-        <v>45.25192793471869</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>524.3220351763848</v>
+        <v>37.49</v>
       </c>
       <c r="Z2" t="n">
-        <v>44.82530923084803</v>
+        <v>527.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>36.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>526.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>46.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>524.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>527.72</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>46.95</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>50.97</v>
       </c>
       <c r="AJ2" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>501.3</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>498.9375</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>499.44</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>498.6083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>497.6357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>497.4</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>497.5777777777778</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>497.845</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>72.00798566825766</v>
+        <v>497.025</v>
       </c>
       <c r="AT2" t="n">
-        <v>66.4038904482762</v>
+        <v>498.35</v>
       </c>
       <c r="AU2" t="n">
-        <v>68.77851113356554</v>
+        <v>497.175</v>
       </c>
       <c r="AV2" t="n">
-        <v>70.74437362787235</v>
+        <v>496.55</v>
       </c>
       <c r="AW2" t="n">
-        <v>67.59305879468855</v>
+        <v>497.925</v>
       </c>
       <c r="AX2" t="n">
-        <v>66.7189425569558</v>
+        <v>497.2928571428571</v>
       </c>
       <c r="AY2" t="n">
-        <v>65.14514563649391</v>
+        <v>497.03125</v>
       </c>
       <c r="AZ2" t="n">
-        <v>62.51701595526308</v>
+        <v>496.3833333333333</v>
       </c>
       <c r="BA2" t="n">
-        <v>60.05648154029672</v>
+        <v>495.82</v>
       </c>
       <c r="BB2" t="n">
-        <v>374</v>
+        <v>61.04608402674164</v>
       </c>
       <c r="BC2" t="n">
-        <v>374</v>
+        <v>60.87496064338221</v>
       </c>
       <c r="BD2" t="n">
-        <v>374</v>
+        <v>59.72934266338446</v>
       </c>
       <c r="BE2" t="n">
-        <v>374</v>
+        <v>58.181676668862</v>
       </c>
       <c r="BF2" t="n">
-        <v>374</v>
+        <v>59.26791747367766</v>
       </c>
       <c r="BG2" t="n">
-        <v>374</v>
+        <v>62.05372055480539</v>
       </c>
       <c r="BH2" t="n">
-        <v>374</v>
+        <v>65.74262523992711</v>
       </c>
       <c r="BI2" t="n">
-        <v>374</v>
+        <v>64.46465655259821</v>
       </c>
       <c r="BJ2" t="n">
-        <v>374</v>
+        <v>63.38452176990847</v>
       </c>
       <c r="BK2" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BL2" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BM2" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BN2" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BO2" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BP2" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BQ2" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BR2" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BS2" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.9166666666666666</v>
+        <v>639</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.9333333333333333</v>
+        <v>639</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.6666666666666666</v>
+        <v>639</v>
       </c>
       <c r="BZ2" t="n">
+        <v>639</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>639</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>639</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CD2" t="n">
         <v>1</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CE2" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CJ2" t="n">
         <v>0.6896551724137931</v>
       </c>
-      <c r="CB2" t="n">
-        <v>0.6363636363636364</v>
+      <c r="CK2" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>532</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>50.97</v>
       </c>
     </row>
     <row r="3">
@@ -1086,10 +1174,10 @@
         <v>520</v>
       </c>
       <c r="C3" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D3" t="n">
         <v>39</v>
-      </c>
-      <c r="D3" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E3" t="n">
         <v>520</v>
@@ -1098,244 +1186,277 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>504.3494980794554</v>
-      </c>
-      <c r="J3" t="n">
-        <v>51.91716437195414</v>
-      </c>
-      <c r="K3" t="n">
-        <v>500.0141713709062</v>
-      </c>
-      <c r="L3" t="n">
-        <v>45.06693776335949</v>
-      </c>
-      <c r="M3" t="n">
-        <v>504.7789444695891</v>
-      </c>
-      <c r="N3" t="n">
-        <v>43.67282190401774</v>
-      </c>
-      <c r="O3" t="n">
-        <v>508.3131879758198</v>
-      </c>
-      <c r="P3" t="n">
-        <v>43.78809887938041</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>505.8474434585916</v>
-      </c>
       <c r="R3" t="n">
-        <v>42.9718817655742</v>
+        <v>504.35</v>
       </c>
       <c r="S3" t="n">
-        <v>508.4742133518382</v>
+        <v>51.92</v>
       </c>
       <c r="T3" t="n">
-        <v>43.14022345328411</v>
+        <v>500.01</v>
       </c>
       <c r="U3" t="n">
-        <v>507.7054557189399</v>
+        <v>45.07</v>
       </c>
       <c r="V3" t="n">
-        <v>43.59068268912968</v>
+        <v>504.78</v>
       </c>
       <c r="W3" t="n">
-        <v>511.1847310576217</v>
+        <v>43.67</v>
       </c>
       <c r="X3" t="n">
-        <v>42.36341962308314</v>
+        <v>508.31</v>
       </c>
       <c r="Y3" t="n">
-        <v>510.7175289992728</v>
+        <v>43.79</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.97005314268404</v>
+        <v>505.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>42.97</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>508.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>43.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>507.71</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>43.59</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>511.18</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>42.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>510.72</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>40.97</v>
       </c>
       <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>493.525</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AT3" t="n">
         <v>497.05</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AU3" t="n">
         <v>496.8375</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AV3" t="n">
         <v>497.59</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AW3" t="n">
         <v>498.7333333333333</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AX3" t="n">
         <v>497.7785714285714</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AY3" t="n">
         <v>497.225</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AZ3" t="n">
         <v>497.3611111111111</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="BA3" t="n">
         <v>497.605</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="BB3" t="n">
         <v>72.59476134680794</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="BC3" t="n">
         <v>64.66488614387255</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="BD3" t="n">
         <v>60.43145781585945</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="BE3" t="n">
         <v>57.90787424867192</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="BF3" t="n">
         <v>57.15457598089199</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="BG3" t="n">
         <v>56.71911593320984</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BH3" t="n">
         <v>55.21978246063633</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BI3" t="n">
         <v>54.36663232053778</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BJ3" t="n">
         <v>52.89167207604615</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BK3" t="n">
         <v>326</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BL3" t="n">
         <v>326</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BM3" t="n">
         <v>326</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BN3" t="n">
         <v>326</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BO3" t="n">
         <v>326</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BP3" t="n">
         <v>326</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BQ3" t="n">
         <v>326</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BR3" t="n">
         <v>326</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BS3" t="n">
         <v>326</v>
       </c>
-      <c r="BK3" t="n">
+      <c r="BT3" t="n">
         <v>582</v>
       </c>
-      <c r="BL3" t="n">
+      <c r="BU3" t="n">
         <v>582</v>
       </c>
-      <c r="BM3" t="n">
+      <c r="BV3" t="n">
         <v>582</v>
       </c>
-      <c r="BN3" t="n">
+      <c r="BW3" t="n">
         <v>582</v>
       </c>
-      <c r="BO3" t="n">
+      <c r="BX3" t="n">
         <v>582</v>
       </c>
-      <c r="BP3" t="n">
+      <c r="BY3" t="n">
         <v>582</v>
       </c>
-      <c r="BQ3" t="n">
+      <c r="BZ3" t="n">
         <v>582</v>
       </c>
-      <c r="BR3" t="n">
+      <c r="CA3" t="n">
         <v>582</v>
       </c>
-      <c r="BS3" t="n">
+      <c r="CB3" t="n">
         <v>582</v>
       </c>
-      <c r="BT3" t="n">
+      <c r="CC3" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="BU3" t="n">
+      <c r="CD3" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BV3" t="n">
+      <c r="CE3" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BW3" t="n">
+      <c r="CF3" t="n">
         <v>1</v>
       </c>
-      <c r="BX3" t="n">
+      <c r="CG3" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" t="n">
+      <c r="CH3" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BZ3" t="n">
+      <c r="CI3" t="n">
         <v>0.76</v>
       </c>
-      <c r="CA3" t="n">
+      <c r="CJ3" t="n">
         <v>0.6551724137931034</v>
       </c>
-      <c r="CB3" t="n">
+      <c r="CK3" t="n">
         <v>0.6551724137931034</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>510.72</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>40.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S01_G8_521_40_REL1</t>
+          <t>S03_G8_521_42_REL1</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>521</v>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D4" t="n">
-        <v>59.30318754633062</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
         <v>521</v>
@@ -1344,720 +1465,819 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>521.015813582366</v>
-      </c>
-      <c r="J4" t="n">
-        <v>51.11353947921182</v>
-      </c>
-      <c r="K4" t="n">
-        <v>518.7112235984052</v>
-      </c>
-      <c r="L4" t="n">
-        <v>47.28910696233856</v>
-      </c>
-      <c r="M4" t="n">
-        <v>520.8279155054321</v>
-      </c>
-      <c r="N4" t="n">
-        <v>41.65011592201621</v>
-      </c>
-      <c r="O4" t="n">
-        <v>525.1768368377654</v>
-      </c>
-      <c r="P4" t="n">
-        <v>37.4931661827907</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>527.148590922097</v>
-      </c>
       <c r="R4" t="n">
-        <v>36.43629247857799</v>
+        <v>529.4299999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>526.3296964234701</v>
+        <v>52.08</v>
       </c>
       <c r="T4" t="n">
-        <v>46.18090708100846</v>
+        <v>513.6900000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>524.1613531326001</v>
+        <v>48.39</v>
       </c>
       <c r="V4" t="n">
-        <v>49.49619004554823</v>
+        <v>515.36</v>
       </c>
       <c r="W4" t="n">
-        <v>527.7151593982028</v>
+        <v>54.9</v>
       </c>
       <c r="X4" t="n">
-        <v>46.94875352228777</v>
+        <v>521.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>531.9967640631993</v>
+        <v>57.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>50.97164097658442</v>
+        <v>525.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>52.49</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>525.5700000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>48.54</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>46.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>527.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>45.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>524.3200000000001</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>44.83</v>
       </c>
       <c r="AJ4" t="n">
-        <v>497.025</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>498.35</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>497.175</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>496.55</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>497.925</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>497.2928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>497.03125</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>496.3833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>495.82</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>61.04608402674164</v>
+        <v>502</v>
       </c>
       <c r="AT4" t="n">
-        <v>60.87496064338221</v>
+        <v>501.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>59.72934266338446</v>
+        <v>498.9375</v>
       </c>
       <c r="AV4" t="n">
-        <v>58.181676668862</v>
+        <v>499.44</v>
       </c>
       <c r="AW4" t="n">
-        <v>59.26791747367766</v>
+        <v>498.6083333333333</v>
       </c>
       <c r="AX4" t="n">
-        <v>62.05372055480539</v>
+        <v>497.6357142857143</v>
       </c>
       <c r="AY4" t="n">
-        <v>65.74262523992711</v>
+        <v>497.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>64.46465655259821</v>
+        <v>497.5777777777778</v>
       </c>
       <c r="BA4" t="n">
-        <v>63.38452176990847</v>
+        <v>497.845</v>
       </c>
       <c r="BB4" t="n">
-        <v>327</v>
+        <v>72.00798566825766</v>
       </c>
       <c r="BC4" t="n">
-        <v>327</v>
+        <v>66.4038904482762</v>
       </c>
       <c r="BD4" t="n">
-        <v>327</v>
+        <v>68.77851113356554</v>
       </c>
       <c r="BE4" t="n">
-        <v>327</v>
+        <v>70.74437362787235</v>
       </c>
       <c r="BF4" t="n">
-        <v>327</v>
+        <v>67.59305879468855</v>
       </c>
       <c r="BG4" t="n">
-        <v>327</v>
+        <v>66.7189425569558</v>
       </c>
       <c r="BH4" t="n">
-        <v>327</v>
+        <v>65.14514563649391</v>
       </c>
       <c r="BI4" t="n">
-        <v>327</v>
+        <v>62.51701595526308</v>
       </c>
       <c r="BJ4" t="n">
-        <v>327</v>
+        <v>60.05648154029672</v>
       </c>
       <c r="BK4" t="n">
-        <v>639</v>
+        <v>374</v>
       </c>
       <c r="BL4" t="n">
-        <v>639</v>
+        <v>374</v>
       </c>
       <c r="BM4" t="n">
-        <v>639</v>
+        <v>374</v>
       </c>
       <c r="BN4" t="n">
-        <v>639</v>
+        <v>374</v>
       </c>
       <c r="BO4" t="n">
-        <v>639</v>
+        <v>374</v>
       </c>
       <c r="BP4" t="n">
-        <v>639</v>
+        <v>374</v>
       </c>
       <c r="BQ4" t="n">
-        <v>639</v>
+        <v>374</v>
       </c>
       <c r="BR4" t="n">
-        <v>639</v>
+        <v>374</v>
       </c>
       <c r="BS4" t="n">
-        <v>639</v>
+        <v>374</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.5555555555555556</v>
+        <v>669</v>
       </c>
       <c r="BU4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CI4" t="n">
         <v>1</v>
       </c>
-      <c r="BV4" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0.7894736842105263</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.8095238095238095</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.6896551724137931</v>
       </c>
-      <c r="CB4" t="n">
-        <v>0.6896551724137931</v>
+      <c r="CK4" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>524.3200000000001</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>44.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S05_G8_518_41_REL1</t>
+          <t>S04_G8_520_40_REL1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D5" t="n">
-        <v>60.78576723498888</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>540.9597043559517</v>
-      </c>
-      <c r="J5" t="n">
-        <v>47.42265884058075</v>
-      </c>
-      <c r="K5" t="n">
-        <v>515.8110841699885</v>
-      </c>
-      <c r="L5" t="n">
-        <v>54.68045085565402</v>
-      </c>
-      <c r="M5" t="n">
-        <v>517.1426933039634</v>
-      </c>
-      <c r="N5" t="n">
-        <v>49.75431752505425</v>
-      </c>
-      <c r="O5" t="n">
-        <v>518.245708589139</v>
-      </c>
-      <c r="P5" t="n">
-        <v>46.78996441017861</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>521.6883468598081</v>
-      </c>
       <c r="R5" t="n">
-        <v>44.38423115172506</v>
+        <v>531.64</v>
       </c>
       <c r="S5" t="n">
-        <v>512.6320862137725</v>
+        <v>36.85</v>
       </c>
       <c r="T5" t="n">
-        <v>48.17946159927348</v>
+        <v>526.14</v>
       </c>
       <c r="U5" t="n">
-        <v>512.444461018994</v>
+        <v>38.49</v>
       </c>
       <c r="V5" t="n">
-        <v>48.21141409702116</v>
+        <v>520.65</v>
       </c>
       <c r="W5" t="n">
-        <v>513.1211033339123</v>
+        <v>48.46</v>
       </c>
       <c r="X5" t="n">
-        <v>45.99322988848942</v>
+        <v>512.46</v>
       </c>
       <c r="Y5" t="n">
-        <v>513.3156536174768</v>
+        <v>50.59</v>
       </c>
       <c r="Z5" t="n">
-        <v>45.26860809147551</v>
+        <v>508.31</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>47.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>46.82</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>507.92</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>45.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>513.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>50.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>511.38</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>47.41</v>
       </c>
       <c r="AJ5" t="n">
-        <v>499.8</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>500.7875</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>503.23</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>502.6166666666667</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>500.7785714285714</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>499.23125</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>498</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>497.715</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>79.26827864915447</v>
+        <v>501.65</v>
       </c>
       <c r="AT5" t="n">
-        <v>71.46794153091767</v>
+        <v>501.4833333333333</v>
       </c>
       <c r="AU5" t="n">
-        <v>65.70401314798055</v>
+        <v>501.65</v>
       </c>
       <c r="AV5" t="n">
-        <v>64.47462369025507</v>
+        <v>500.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>60.93482629462034</v>
+        <v>499.1083333333333</v>
       </c>
       <c r="AX5" t="n">
-        <v>61.35226947218623</v>
+        <v>498.9714285714286</v>
       </c>
       <c r="AY5" t="n">
-        <v>61.39821066967261</v>
+        <v>498.65625</v>
       </c>
       <c r="AZ5" t="n">
-        <v>60.53951877355264</v>
+        <v>498.35</v>
       </c>
       <c r="BA5" t="n">
-        <v>59.85719484740326</v>
+        <v>498.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>374</v>
+        <v>66.41631953066957</v>
       </c>
       <c r="BC5" t="n">
-        <v>374</v>
+        <v>59.68374755511103</v>
       </c>
       <c r="BD5" t="n">
-        <v>374</v>
+        <v>69.46547703715854</v>
       </c>
       <c r="BE5" t="n">
-        <v>374</v>
+        <v>69.67655200998396</v>
       </c>
       <c r="BF5" t="n">
-        <v>374</v>
+        <v>66.06597659831336</v>
       </c>
       <c r="BG5" t="n">
-        <v>374</v>
+        <v>63.90852199568904</v>
       </c>
       <c r="BH5" t="n">
-        <v>374</v>
+        <v>62.01653477853709</v>
       </c>
       <c r="BI5" t="n">
-        <v>374</v>
+        <v>62.27497044916556</v>
       </c>
       <c r="BJ5" t="n">
-        <v>374</v>
+        <v>61.32714814827117</v>
       </c>
       <c r="BK5" t="n">
-        <v>669</v>
+        <v>394</v>
       </c>
       <c r="BL5" t="n">
-        <v>669</v>
+        <v>394</v>
       </c>
       <c r="BM5" t="n">
-        <v>669</v>
+        <v>393</v>
       </c>
       <c r="BN5" t="n">
-        <v>669</v>
+        <v>393</v>
       </c>
       <c r="BO5" t="n">
-        <v>669</v>
+        <v>393</v>
       </c>
       <c r="BP5" t="n">
-        <v>669</v>
+        <v>393</v>
       </c>
       <c r="BQ5" t="n">
-        <v>669</v>
+        <v>393</v>
       </c>
       <c r="BR5" t="n">
-        <v>669</v>
+        <v>393</v>
       </c>
       <c r="BS5" t="n">
-        <v>669</v>
+        <v>393</v>
       </c>
       <c r="BT5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="BU5" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.8636363636363636</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.9166666666666666</v>
+      <c r="CD5" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>511.38</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>47.41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S04_G8_520_40_REL1</t>
+          <t>S05_G8_518_41_REL1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D6" t="n">
-        <v>59.30318754633062</v>
+        <v>41</v>
       </c>
       <c r="E6" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>531.6449254647989</v>
-      </c>
-      <c r="J6" t="n">
-        <v>36.8481509917895</v>
-      </c>
-      <c r="K6" t="n">
-        <v>526.1365934276822</v>
-      </c>
-      <c r="L6" t="n">
-        <v>38.49156554481185</v>
-      </c>
-      <c r="M6" t="n">
-        <v>520.6516251025025</v>
-      </c>
-      <c r="N6" t="n">
-        <v>48.46165282936153</v>
-      </c>
-      <c r="O6" t="n">
-        <v>512.4580731705356</v>
-      </c>
-      <c r="P6" t="n">
-        <v>50.59074345504592</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>508.3072241980679</v>
-      </c>
       <c r="R6" t="n">
-        <v>47.32790717094008</v>
+        <v>540.96</v>
       </c>
       <c r="S6" t="n">
-        <v>509.998486424873</v>
+        <v>47.42</v>
       </c>
       <c r="T6" t="n">
-        <v>46.81729006332656</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>507.9216850429486</v>
+        <v>54.68</v>
       </c>
       <c r="V6" t="n">
-        <v>45.35523176466693</v>
+        <v>517.14</v>
       </c>
       <c r="W6" t="n">
-        <v>513.70908738214</v>
+        <v>49.75</v>
       </c>
       <c r="X6" t="n">
-        <v>50.26078018325711</v>
+        <v>518.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>511.3781780292986</v>
+        <v>46.79</v>
       </c>
       <c r="Z6" t="n">
-        <v>47.40684512372244</v>
+        <v>521.6900000000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>44.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>512.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>48.18</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>512.4400000000001</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>48.21</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>513.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>45.99</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>513.3200000000001</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>45.27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>501.65</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>501.4833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>501.65</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>500.09</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>499.1083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>498.9714285714286</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>498.65625</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>498.35</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>498.03</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>66.41631953066957</v>
+        <v>499.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>59.68374755511103</v>
+        <v>501</v>
       </c>
       <c r="AU6" t="n">
-        <v>69.46547703715854</v>
+        <v>500.7875</v>
       </c>
       <c r="AV6" t="n">
-        <v>69.67655200998396</v>
+        <v>503.23</v>
       </c>
       <c r="AW6" t="n">
-        <v>66.06597659831336</v>
+        <v>502.6166666666667</v>
       </c>
       <c r="AX6" t="n">
-        <v>63.90852199568904</v>
+        <v>500.7785714285714</v>
       </c>
       <c r="AY6" t="n">
-        <v>62.01653477853709</v>
+        <v>499.23125</v>
       </c>
       <c r="AZ6" t="n">
-        <v>62.27497044916556</v>
+        <v>498</v>
       </c>
       <c r="BA6" t="n">
-        <v>61.32714814827117</v>
+        <v>497.715</v>
       </c>
       <c r="BB6" t="n">
-        <v>394</v>
+        <v>79.26827864915447</v>
       </c>
       <c r="BC6" t="n">
-        <v>394</v>
+        <v>71.46794153091767</v>
       </c>
       <c r="BD6" t="n">
-        <v>393</v>
+        <v>65.70401314798055</v>
       </c>
       <c r="BE6" t="n">
-        <v>393</v>
+        <v>64.47462369025507</v>
       </c>
       <c r="BF6" t="n">
-        <v>393</v>
+        <v>60.93482629462034</v>
       </c>
       <c r="BG6" t="n">
-        <v>393</v>
+        <v>61.35226947218623</v>
       </c>
       <c r="BH6" t="n">
-        <v>393</v>
+        <v>61.39821066967261</v>
       </c>
       <c r="BI6" t="n">
-        <v>393</v>
+        <v>60.53951877355264</v>
       </c>
       <c r="BJ6" t="n">
-        <v>393</v>
+        <v>59.85719484740326</v>
       </c>
       <c r="BK6" t="n">
-        <v>669</v>
+        <v>374</v>
       </c>
       <c r="BL6" t="n">
-        <v>669</v>
+        <v>374</v>
       </c>
       <c r="BM6" t="n">
-        <v>669</v>
+        <v>374</v>
       </c>
       <c r="BN6" t="n">
-        <v>669</v>
+        <v>374</v>
       </c>
       <c r="BO6" t="n">
-        <v>669</v>
+        <v>374</v>
       </c>
       <c r="BP6" t="n">
-        <v>669</v>
+        <v>374</v>
       </c>
       <c r="BQ6" t="n">
-        <v>669</v>
+        <v>374</v>
       </c>
       <c r="BR6" t="n">
-        <v>669</v>
+        <v>374</v>
       </c>
       <c r="BS6" t="n">
-        <v>669</v>
+        <v>374</v>
       </c>
       <c r="BT6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="BU6" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0.8461538461538461</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.8333333333333334</v>
+      <c r="CD6" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>513.3200000000001</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>45.27</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>520</v>
       </c>
       <c r="C7" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D7" t="n">
         <v>42</v>
-      </c>
-      <c r="D7" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E7" t="n">
         <v>520</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>519.493485978235</v>
-      </c>
-      <c r="J7" t="n">
-        <v>33.31088934791244</v>
-      </c>
-      <c r="K7" t="n">
-        <v>535.0695956470468</v>
-      </c>
-      <c r="L7" t="n">
-        <v>48.26920451689178</v>
-      </c>
-      <c r="M7" t="n">
-        <v>531.6336529409658</v>
-      </c>
-      <c r="N7" t="n">
-        <v>40.34230830110668</v>
-      </c>
-      <c r="O7" t="n">
-        <v>531.3445364126126</v>
-      </c>
-      <c r="P7" t="n">
-        <v>35.89893346299894</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>527.4152515654453</v>
-      </c>
       <c r="R7" t="n">
-        <v>43.04413820876068</v>
+        <v>519.49</v>
       </c>
       <c r="S7" t="n">
-        <v>527.1207335763023</v>
+        <v>33.31</v>
       </c>
       <c r="T7" t="n">
-        <v>41.56007692674367</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>529.712883798098</v>
+        <v>48.27</v>
       </c>
       <c r="V7" t="n">
-        <v>46.87092601069502</v>
+        <v>531.63</v>
       </c>
       <c r="W7" t="n">
-        <v>530.8853032868994</v>
+        <v>40.34</v>
       </c>
       <c r="X7" t="n">
-        <v>45.91388206212672</v>
+        <v>531.34</v>
       </c>
       <c r="Y7" t="n">
-        <v>531.8526317989465</v>
+        <v>35.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>47.09257607933938</v>
+        <v>527.42</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>43.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>527.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>41.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>529.71</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>46.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>530.89</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>45.91</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>531.85</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>47.09</v>
       </c>
       <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>495.375</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>494.7833333333334</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>495.925</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>496.2</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>497.3666666666667</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>498.0714285714286</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>497.93125</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>498.65</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>498.39</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>57.35882124834854</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>55.64533273829492</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>57.47581556620141</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>57.06259720692706</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>56.5741303266981</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>56.4389231011394</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>59.40645186709521</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>62.52710301230268</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>63.96716266960729</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>349</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>349</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>349</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>349</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>349</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>349</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>349</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>349</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>349</v>
       </c>
-      <c r="BK7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>669</v>
-      </c>
       <c r="BT7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.875</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>1</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>1</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>0.9615384615384616</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>531.85</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>47.09</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>520</v>
       </c>
       <c r="C8" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D8" t="n">
         <v>39</v>
-      </c>
-      <c r="D8" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E8" t="n">
         <v>520</v>
@@ -2328,720 +2581,819 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>500.1946153199201</v>
-      </c>
-      <c r="J8" t="n">
-        <v>61.70311323217898</v>
-      </c>
-      <c r="K8" t="n">
-        <v>496.4670644269877</v>
-      </c>
-      <c r="L8" t="n">
-        <v>53.34931036611279</v>
-      </c>
-      <c r="M8" t="n">
-        <v>501.2319363620193</v>
-      </c>
-      <c r="N8" t="n">
-        <v>50.98622362682218</v>
-      </c>
-      <c r="O8" t="n">
-        <v>508.2629472110579</v>
-      </c>
-      <c r="P8" t="n">
-        <v>47.99331966896924</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>505.6488803945356</v>
-      </c>
       <c r="R8" t="n">
-        <v>46.78037612421887</v>
+        <v>500.19</v>
       </c>
       <c r="S8" t="n">
-        <v>505.4112932610014</v>
+        <v>61.7</v>
       </c>
       <c r="T8" t="n">
-        <v>47.27754451759113</v>
+        <v>496.47</v>
       </c>
       <c r="U8" t="n">
-        <v>507.324152348059</v>
+        <v>53.35</v>
       </c>
       <c r="V8" t="n">
-        <v>43.47144574642436</v>
+        <v>501.23</v>
       </c>
       <c r="W8" t="n">
-        <v>505.0445611831241</v>
+        <v>50.99</v>
       </c>
       <c r="X8" t="n">
-        <v>42.74282951598092</v>
+        <v>508.26</v>
       </c>
       <c r="Y8" t="n">
-        <v>507.5217212020522</v>
+        <v>47.99</v>
       </c>
       <c r="Z8" t="n">
-        <v>42.9865259825894</v>
+        <v>505.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>46.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>505.41</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>47.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>507.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>43.47</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>505.04</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>42.74</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>507.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>42.99</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>500.825</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>501.3333333333333</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>501.2875</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>501.56</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>502.0833333333333</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>502.3071428571429</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>501.8125</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>501.6222222222222</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>501.435</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>74.34476696446093</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>67.89738990237809</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>63.47089761260668</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>60.36163019667379</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>58.94893034558718</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>57.64099439369413</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>57.23451619215454</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>54.74944500536112</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>53.65357187550518</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>366</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>366</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>366</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>366</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>366</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>366</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>366</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>366</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>366</v>
       </c>
-      <c r="BK8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>669</v>
-      </c>
       <c r="BT8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.8</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.875</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.7741935483870968</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.7878787878787878</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>507.52</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>42.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S09_G8_521_38_REL1</t>
+          <t>S08_G8_520_42_REL1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D9" t="n">
-        <v>56.33802816901409</v>
+        <v>42</v>
       </c>
       <c r="E9" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F9" t="n">
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>503.5414963920189</v>
-      </c>
-      <c r="J9" t="n">
-        <v>45.6021491206647</v>
-      </c>
-      <c r="K9" t="n">
-        <v>510.0546590298077</v>
-      </c>
-      <c r="L9" t="n">
-        <v>40.8855892247168</v>
-      </c>
-      <c r="M9" t="n">
-        <v>519.3237542501114</v>
-      </c>
-      <c r="N9" t="n">
-        <v>38.75701846744851</v>
-      </c>
-      <c r="O9" t="n">
-        <v>525.9655669923511</v>
-      </c>
-      <c r="P9" t="n">
-        <v>36.03792451042254</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>526.5979738275137</v>
-      </c>
       <c r="R9" t="n">
-        <v>40.80016975049951</v>
+        <v>508.19</v>
       </c>
       <c r="S9" t="n">
-        <v>526.2502034435034</v>
+        <v>57.77</v>
       </c>
       <c r="T9" t="n">
-        <v>43.28130190398377</v>
+        <v>512.13</v>
       </c>
       <c r="U9" t="n">
-        <v>527.5446850993654</v>
+        <v>53.86</v>
       </c>
       <c r="V9" t="n">
-        <v>40.70477279319613</v>
+        <v>509.43</v>
       </c>
       <c r="W9" t="n">
-        <v>528.6353102104631</v>
+        <v>64.8</v>
       </c>
       <c r="X9" t="n">
-        <v>42.08761945290802</v>
+        <v>508.18</v>
       </c>
       <c r="Y9" t="n">
-        <v>529.2612952524584</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>43.37154267802491</v>
+        <v>506.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>508.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>68.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>506.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>63.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>501.56</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>61.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>503.73</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>59.86</v>
       </c>
       <c r="AJ9" t="n">
-        <v>497.2</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>497.6</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>496.8875</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>498.09</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>497.3833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>497.2</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>500.3</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>498.2333333333333</v>
+      </c>
+      <c r="AU9" t="n">
         <v>497.975</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>497.3333333333333</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>496.96</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>60.4599867681097</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>61.55192929551437</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>57.94932996808505</v>
-      </c>
       <c r="AV9" t="n">
-        <v>55.90296861527123</v>
+        <v>498.37</v>
       </c>
       <c r="AW9" t="n">
-        <v>55.89531634125429</v>
+        <v>501.2416666666667</v>
       </c>
       <c r="AX9" t="n">
-        <v>56.3630071183979</v>
+        <v>503.2714285714285</v>
       </c>
       <c r="AY9" t="n">
-        <v>56.7232260630511</v>
+        <v>502.0625</v>
       </c>
       <c r="AZ9" t="n">
-        <v>56.81617531810618</v>
+        <v>501.5444444444444</v>
       </c>
       <c r="BA9" t="n">
-        <v>58.166987200645</v>
+        <v>500.84</v>
       </c>
       <c r="BB9" t="n">
-        <v>330</v>
+        <v>78.83152922530427</v>
       </c>
       <c r="BC9" t="n">
-        <v>330</v>
+        <v>70.18626804598048</v>
       </c>
       <c r="BD9" t="n">
-        <v>330</v>
+        <v>77.61619917903737</v>
       </c>
       <c r="BE9" t="n">
-        <v>330</v>
+        <v>85.43238905707834</v>
       </c>
       <c r="BF9" t="n">
-        <v>330</v>
+        <v>81.56367613030257</v>
       </c>
       <c r="BG9" t="n">
-        <v>330</v>
+        <v>81.90018688772876</v>
       </c>
       <c r="BH9" t="n">
-        <v>330</v>
+        <v>80.51402731046311</v>
       </c>
       <c r="BI9" t="n">
-        <v>330</v>
+        <v>78.46296523571006</v>
       </c>
       <c r="BJ9" t="n">
-        <v>330</v>
+        <v>77.74030100276175</v>
       </c>
       <c r="BK9" t="n">
-        <v>637</v>
+        <v>351</v>
       </c>
       <c r="BL9" t="n">
-        <v>637</v>
+        <v>351</v>
       </c>
       <c r="BM9" t="n">
-        <v>637</v>
+        <v>351</v>
       </c>
       <c r="BN9" t="n">
-        <v>637</v>
+        <v>351</v>
       </c>
       <c r="BO9" t="n">
-        <v>637</v>
+        <v>351</v>
       </c>
       <c r="BP9" t="n">
-        <v>637</v>
+        <v>351</v>
       </c>
       <c r="BQ9" t="n">
-        <v>637</v>
+        <v>351</v>
       </c>
       <c r="BR9" t="n">
-        <v>637</v>
+        <v>351</v>
       </c>
       <c r="BS9" t="n">
-        <v>637</v>
+        <v>351</v>
       </c>
       <c r="BT9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CJ9" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.8695652173913043</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.8461538461538461</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>1</v>
+      <c r="CK9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>503.73</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>59.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S08_G8_520_42_REL1</t>
+          <t>S09_G8_521_38_REL1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D10" t="n">
-        <v>62.26834692364714</v>
+        <v>38</v>
       </c>
       <c r="E10" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F10" t="n">
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>508.1943058345774</v>
-      </c>
-      <c r="J10" t="n">
-        <v>57.76857333337129</v>
-      </c>
-      <c r="K10" t="n">
-        <v>512.1280584405259</v>
-      </c>
-      <c r="L10" t="n">
-        <v>53.86239176510197</v>
-      </c>
-      <c r="M10" t="n">
-        <v>509.4287084751013</v>
-      </c>
-      <c r="N10" t="n">
-        <v>64.80355167247329</v>
-      </c>
-      <c r="O10" t="n">
-        <v>508.180331572622</v>
-      </c>
-      <c r="P10" t="n">
-        <v>66.23779302959078</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>506.599302489226</v>
-      </c>
       <c r="R10" t="n">
-        <v>65.60360674337996</v>
+        <v>503.54</v>
       </c>
       <c r="S10" t="n">
-        <v>508.0797920447631</v>
+        <v>45.6</v>
       </c>
       <c r="T10" t="n">
-        <v>68.69459164733539</v>
+        <v>510.05</v>
       </c>
       <c r="U10" t="n">
-        <v>506.1043914991985</v>
+        <v>40.89</v>
       </c>
       <c r="V10" t="n">
-        <v>63.62147008611873</v>
+        <v>519.3200000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>501.5642953647854</v>
+        <v>38.76</v>
       </c>
       <c r="X10" t="n">
-        <v>61.27507267514889</v>
+        <v>525.97</v>
       </c>
       <c r="Y10" t="n">
-        <v>503.7334469976649</v>
+        <v>36.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>59.85912184004987</v>
+        <v>526.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>40.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>526.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>43.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>527.54</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>528.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>42.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>529.26</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>43.37</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500.3</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>498.2333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>497.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>497.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>496.8875</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>498.09</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>497.3833333333333</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>497.2</v>
+      </c>
+      <c r="AY10" t="n">
         <v>497.975</v>
       </c>
-      <c r="AM10" t="n">
-        <v>498.37</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>501.2416666666667</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>503.2714285714285</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>502.0625</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>501.5444444444444</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>500.84</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>78.83152922530427</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>70.18626804598048</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>77.61619917903737</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>85.43238905707834</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>81.56367613030257</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>81.90018688772876</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>80.51402731046311</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>78.46296523571006</v>
+        <v>497.3333333333333</v>
       </c>
       <c r="BA10" t="n">
-        <v>77.74030100276175</v>
+        <v>496.96</v>
       </c>
       <c r="BB10" t="n">
-        <v>351</v>
+        <v>60.4599867681097</v>
       </c>
       <c r="BC10" t="n">
-        <v>351</v>
+        <v>61.55192929551437</v>
       </c>
       <c r="BD10" t="n">
-        <v>351</v>
+        <v>57.94932996808505</v>
       </c>
       <c r="BE10" t="n">
-        <v>351</v>
+        <v>55.90296861527123</v>
       </c>
       <c r="BF10" t="n">
-        <v>351</v>
+        <v>55.89531634125429</v>
       </c>
       <c r="BG10" t="n">
-        <v>351</v>
+        <v>56.3630071183979</v>
       </c>
       <c r="BH10" t="n">
-        <v>351</v>
+        <v>56.7232260630511</v>
       </c>
       <c r="BI10" t="n">
-        <v>351</v>
+        <v>56.81617531810618</v>
       </c>
       <c r="BJ10" t="n">
-        <v>351</v>
+        <v>58.166987200645</v>
       </c>
       <c r="BK10" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BL10" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BM10" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BN10" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BO10" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BP10" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BQ10" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BR10" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BS10" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.09090909090909091</v>
+        <v>637</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.8181818181818182</v>
+        <v>637</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.9090909090909091</v>
+        <v>637</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.9166666666666666</v>
+        <v>637</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.6875</v>
+        <v>637</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.7</v>
+        <v>637</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.95</v>
+        <v>637</v>
       </c>
       <c r="CA10" t="n">
+        <v>637</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>637</v>
+      </c>
+      <c r="CC10" t="n">
         <v>0.875</v>
       </c>
-      <c r="CB10" t="n">
-        <v>0.84</v>
+      <c r="CD10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>529.26</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>43.37</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>519</v>
       </c>
       <c r="C11" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D11" t="n">
         <v>39</v>
-      </c>
-      <c r="D11" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E11" t="n">
         <v>519</v>
@@ -3066,244 +3418,277 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>513.8147857906272</v>
-      </c>
-      <c r="J11" t="n">
-        <v>46.8108776673841</v>
-      </c>
-      <c r="K11" t="n">
-        <v>516.9823575939475</v>
-      </c>
-      <c r="L11" t="n">
-        <v>46.35651377460579</v>
-      </c>
-      <c r="M11" t="n">
-        <v>521.6192468776219</v>
-      </c>
-      <c r="N11" t="n">
-        <v>47.72008521507104</v>
-      </c>
-      <c r="O11" t="n">
-        <v>527.4238147709631</v>
-      </c>
-      <c r="P11" t="n">
-        <v>46.05392374850081</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>525.8351832114155</v>
-      </c>
       <c r="R11" t="n">
-        <v>48.73993029304109</v>
+        <v>513.8099999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>525.3556862984855</v>
+        <v>46.81</v>
       </c>
       <c r="T11" t="n">
-        <v>44.92462625696129</v>
+        <v>516.98</v>
       </c>
       <c r="U11" t="n">
-        <v>526.0642860834415</v>
+        <v>46.36</v>
       </c>
       <c r="V11" t="n">
-        <v>42.08501608303958</v>
+        <v>521.62</v>
       </c>
       <c r="W11" t="n">
-        <v>525.6502913044853</v>
+        <v>47.72</v>
       </c>
       <c r="X11" t="n">
-        <v>40.91685563459365</v>
+        <v>527.42</v>
       </c>
       <c r="Y11" t="n">
-        <v>525.1404649063129</v>
+        <v>46.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>40.82858828984698</v>
+        <v>525.84</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>48.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>525.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>44.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>526.0599999999999</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>42.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>525.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>40.92</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>525.14</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>40.83</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>502.05</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>501.0166666666667</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>500.275</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>500.34</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>499.8333333333333</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>499.2142857142857</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>499.3625</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>499.4111111111111</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>499.29</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>65.31345573463403</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>61.75799318486816</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>60.51280339729767</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>60.31040042977662</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>58.20786506611933</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>56.07759747684908</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>53.44781187055275</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>52.22385458441688</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>51.27246727045618</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>364</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>364</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>364</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>364</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>364</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>364</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>364</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>364</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>364</v>
       </c>
-      <c r="BK11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>669</v>
-      </c>
       <c r="BT11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.5757575757575758</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.8947368421052632</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>525.14</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>40.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S12_G8_522_38_REL1</t>
+          <t>S11_G8_522_41_REL1</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>522</v>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D12" t="n">
-        <v>56.33802816901409</v>
+        <v>41</v>
       </c>
       <c r="E12" t="n">
         <v>522</v>
@@ -3312,244 +3697,277 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>546.2445241666572</v>
-      </c>
-      <c r="J12" t="n">
-        <v>46.77639549000769</v>
-      </c>
-      <c r="K12" t="n">
-        <v>534.782401098543</v>
-      </c>
-      <c r="L12" t="n">
-        <v>50.06248493598</v>
-      </c>
-      <c r="M12" t="n">
-        <v>525.4706675512107</v>
-      </c>
-      <c r="N12" t="n">
-        <v>47.61906764989854</v>
-      </c>
-      <c r="O12" t="n">
-        <v>524.0821167095916</v>
-      </c>
-      <c r="P12" t="n">
-        <v>46.8849688581379</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>525.6231694255076</v>
-      </c>
       <c r="R12" t="n">
-        <v>50.78123140082774</v>
+        <v>524.33</v>
       </c>
       <c r="S12" t="n">
-        <v>522.7944106137707</v>
+        <v>27.32</v>
       </c>
       <c r="T12" t="n">
-        <v>48.07424996417117</v>
+        <v>528.26</v>
       </c>
       <c r="U12" t="n">
-        <v>523.2755209586409</v>
+        <v>34.27</v>
       </c>
       <c r="V12" t="n">
-        <v>46.2093359768654</v>
+        <v>530.0700000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>520.7487833724931</v>
+        <v>54.81</v>
       </c>
       <c r="X12" t="n">
-        <v>45.63716619845088</v>
+        <v>528.65</v>
       </c>
       <c r="Y12" t="n">
-        <v>521.8458372095433</v>
+        <v>53.23</v>
       </c>
       <c r="Z12" t="n">
-        <v>44.81451224057653</v>
+        <v>530.4400000000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>50.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>531.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>53.39</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>531.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>55.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>527.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>50.98</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>526.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>51.23</v>
       </c>
       <c r="AJ12" t="n">
-        <v>500.85</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>500.1166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>498.975</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>500.34</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>498.1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>498.2785714285714</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>499.70625</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>499.25</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>497.99</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>76.83409074102458</v>
+        <v>498.725</v>
       </c>
       <c r="AT12" t="n">
-        <v>73.07441222632052</v>
+        <v>498.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>67.10290139032737</v>
+        <v>498.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>61.56073748746031</v>
+        <v>498.79</v>
       </c>
       <c r="AW12" t="n">
-        <v>65.05720559630578</v>
+        <v>498.8416666666666</v>
       </c>
       <c r="AX12" t="n">
-        <v>63.73876011357867</v>
+        <v>499.2642857142857</v>
       </c>
       <c r="AY12" t="n">
-        <v>62.07974678538485</v>
+        <v>499.36875</v>
       </c>
       <c r="AZ12" t="n">
-        <v>60.51242985260686</v>
+        <v>499.6166666666667</v>
       </c>
       <c r="BA12" t="n">
-        <v>60.48181462224823</v>
+        <v>499.48</v>
       </c>
       <c r="BB12" t="n">
-        <v>381</v>
+        <v>59.84270527808715</v>
       </c>
       <c r="BC12" t="n">
-        <v>381</v>
+        <v>55.40740774782135</v>
       </c>
       <c r="BD12" t="n">
-        <v>381</v>
+        <v>53.60209883950441</v>
       </c>
       <c r="BE12" t="n">
-        <v>381</v>
+        <v>54.33494179623274</v>
       </c>
       <c r="BF12" t="n">
-        <v>381</v>
+        <v>57.49536152788521</v>
       </c>
       <c r="BG12" t="n">
-        <v>381</v>
+        <v>60.59804460710001</v>
       </c>
       <c r="BH12" t="n">
-        <v>381</v>
+        <v>65.21221337631088</v>
       </c>
       <c r="BI12" t="n">
-        <v>381</v>
+        <v>66.80770705706207</v>
       </c>
       <c r="BJ12" t="n">
-        <v>381</v>
+        <v>64.4128838044067</v>
       </c>
       <c r="BK12" t="n">
-        <v>669</v>
+        <v>349</v>
       </c>
       <c r="BL12" t="n">
-        <v>669</v>
+        <v>349</v>
       </c>
       <c r="BM12" t="n">
-        <v>669</v>
+        <v>349</v>
       </c>
       <c r="BN12" t="n">
-        <v>669</v>
+        <v>349</v>
       </c>
       <c r="BO12" t="n">
-        <v>669</v>
+        <v>349</v>
       </c>
       <c r="BP12" t="n">
-        <v>669</v>
+        <v>349</v>
       </c>
       <c r="BQ12" t="n">
-        <v>669</v>
+        <v>349</v>
       </c>
       <c r="BR12" t="n">
-        <v>669</v>
+        <v>349</v>
       </c>
       <c r="BS12" t="n">
-        <v>669</v>
+        <v>349</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.5625</v>
+        <v>669</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.6538461538461539</v>
+        <v>669</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.9259259259259259</v>
+        <v>669</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.9</v>
+        <v>669</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>526.38</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>51.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S11_G8_522_41_REL1</t>
+          <t>S12_G8_522_38_REL1</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>522</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D13" t="n">
-        <v>60.78576723498888</v>
+        <v>38</v>
       </c>
       <c r="E13" t="n">
         <v>522</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>524.327218395331</v>
-      </c>
-      <c r="J13" t="n">
-        <v>27.31836109772241</v>
-      </c>
-      <c r="K13" t="n">
-        <v>528.2588905146056</v>
-      </c>
-      <c r="L13" t="n">
-        <v>34.27093857027615</v>
-      </c>
-      <c r="M13" t="n">
-        <v>530.0696948600631</v>
-      </c>
-      <c r="N13" t="n">
-        <v>54.80863716140207</v>
-      </c>
-      <c r="O13" t="n">
-        <v>528.6535412855133</v>
-      </c>
-      <c r="P13" t="n">
-        <v>53.23117422397123</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>530.4385912399538</v>
-      </c>
       <c r="R13" t="n">
-        <v>50.56168597320129</v>
+        <v>546.24</v>
       </c>
       <c r="S13" t="n">
-        <v>531.5485159130235</v>
+        <v>46.78</v>
       </c>
       <c r="T13" t="n">
-        <v>53.38815363218306</v>
+        <v>534.78</v>
       </c>
       <c r="U13" t="n">
-        <v>531.1654512552684</v>
+        <v>50.06</v>
       </c>
       <c r="V13" t="n">
-        <v>55.29593360122075</v>
+        <v>525.47</v>
       </c>
       <c r="W13" t="n">
-        <v>527.9507270258846</v>
+        <v>47.62</v>
       </c>
       <c r="X13" t="n">
-        <v>50.98313180181595</v>
+        <v>524.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>526.381453279074</v>
+        <v>46.88</v>
       </c>
       <c r="Z13" t="n">
-        <v>51.22733249704161</v>
+        <v>525.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>50.78</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>522.79</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>48.07</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>523.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>46.21</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>520.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>45.64</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>521.85</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>44.81</v>
       </c>
       <c r="AJ13" t="n">
-        <v>498.725</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>498.45</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>498.8</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>498.79</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>498.8416666666666</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>499.2642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>499.36875</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>499.6166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>499.48</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>59.84270527808715</v>
+        <v>500.85</v>
       </c>
       <c r="AT13" t="n">
-        <v>55.40740774782135</v>
+        <v>500.1166666666667</v>
       </c>
       <c r="AU13" t="n">
-        <v>53.60209883950441</v>
+        <v>498.975</v>
       </c>
       <c r="AV13" t="n">
-        <v>54.33494179623274</v>
+        <v>500.34</v>
       </c>
       <c r="AW13" t="n">
-        <v>57.49536152788521</v>
+        <v>498.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>60.59804460710001</v>
+        <v>498.2785714285714</v>
       </c>
       <c r="AY13" t="n">
-        <v>65.21221337631088</v>
+        <v>499.70625</v>
       </c>
       <c r="AZ13" t="n">
-        <v>66.80770705706207</v>
+        <v>499.25</v>
       </c>
       <c r="BA13" t="n">
-        <v>64.4128838044067</v>
+        <v>497.99</v>
       </c>
       <c r="BB13" t="n">
-        <v>349</v>
+        <v>76.83409074102458</v>
       </c>
       <c r="BC13" t="n">
-        <v>349</v>
+        <v>73.07441222632052</v>
       </c>
       <c r="BD13" t="n">
-        <v>349</v>
+        <v>67.10290139032737</v>
       </c>
       <c r="BE13" t="n">
-        <v>349</v>
+        <v>61.56073748746031</v>
       </c>
       <c r="BF13" t="n">
-        <v>349</v>
+        <v>65.05720559630578</v>
       </c>
       <c r="BG13" t="n">
-        <v>349</v>
+        <v>63.73876011357867</v>
       </c>
       <c r="BH13" t="n">
-        <v>349</v>
+        <v>62.07974678538485</v>
       </c>
       <c r="BI13" t="n">
-        <v>349</v>
+        <v>60.51242985260686</v>
       </c>
       <c r="BJ13" t="n">
-        <v>349</v>
+        <v>60.48181462224823</v>
       </c>
       <c r="BK13" t="n">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="BL13" t="n">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="BM13" t="n">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="BN13" t="n">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="BO13" t="n">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="BP13" t="n">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="BQ13" t="n">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="BR13" t="n">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="BS13" t="n">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.7333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.6</v>
+        <v>669</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.6129032258064516</v>
+        <v>669</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.6451612903225806</v>
+        <v>669</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.6774193548387096</v>
+        <v>669</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.6774193548387096</v>
+        <v>669</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.6774193548387096</v>
+        <v>669</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.6774193548387096</v>
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>521.85</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>44.81</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>522</v>
       </c>
       <c r="C14" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E14" t="n">
         <v>522</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>510.4518069465003</v>
-      </c>
-      <c r="J14" t="n">
-        <v>39.38101319819758</v>
-      </c>
-      <c r="K14" t="n">
-        <v>530.0835281402319</v>
-      </c>
-      <c r="L14" t="n">
-        <v>37.75375319001687</v>
-      </c>
-      <c r="M14" t="n">
-        <v>517.9988518284646</v>
-      </c>
-      <c r="N14" t="n">
-        <v>39.7667138878729</v>
-      </c>
-      <c r="O14" t="n">
-        <v>519.3705880263745</v>
-      </c>
-      <c r="P14" t="n">
-        <v>38.74729166803645</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>521.4769297067181</v>
-      </c>
       <c r="R14" t="n">
-        <v>41.35330286810789</v>
+        <v>510.45</v>
       </c>
       <c r="S14" t="n">
-        <v>516.0554094326592</v>
+        <v>39.38</v>
       </c>
       <c r="T14" t="n">
-        <v>39.63215758429545</v>
+        <v>530.08</v>
       </c>
       <c r="U14" t="n">
-        <v>518.9443948966619</v>
+        <v>37.75</v>
       </c>
       <c r="V14" t="n">
-        <v>39.39854961235888</v>
+        <v>518</v>
       </c>
       <c r="W14" t="n">
-        <v>519.5811533772176</v>
+        <v>39.77</v>
       </c>
       <c r="X14" t="n">
-        <v>39.49452102929523</v>
+        <v>519.37</v>
       </c>
       <c r="Y14" t="n">
-        <v>518.8190893751952</v>
+        <v>38.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>41.50156849516901</v>
+        <v>521.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>41.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>516.0599999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>39.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>518.9400000000001</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>39.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>519.58</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>39.49</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>518.8200000000001</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>41.5</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>493.85</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>496.8333333333333</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>496.4</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>494.78</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>497.425</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>498.8142857142857</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>498.65625</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>499.1555555555556</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>499.99</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>66.85602067129032</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>60.07472199038646</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>57.300218149672</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>54.28767447588817</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>54.51217944948939</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>53.88818923266498</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>54.61765361069166</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>54.47770412667535</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>54.77344155701739</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>344</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>344</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>344</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>344</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>344</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>344</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>344</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>344</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>344</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BT14" t="n">
         <v>589</v>
       </c>
-      <c r="BL14" t="n">
+      <c r="BU14" t="n">
         <v>589</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BV14" t="n">
         <v>589</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BW14" t="n">
         <v>589</v>
       </c>
-      <c r="BO14" t="n">
+      <c r="BX14" t="n">
         <v>589</v>
       </c>
-      <c r="BP14" t="n">
+      <c r="BY14" t="n">
         <v>589</v>
       </c>
-      <c r="BQ14" t="n">
+      <c r="BZ14" t="n">
         <v>589</v>
       </c>
-      <c r="BR14" t="n">
+      <c r="CA14" t="n">
         <v>589</v>
       </c>
-      <c r="BS14" t="n">
+      <c r="CB14" t="n">
         <v>589</v>
       </c>
-      <c r="BT14" t="n">
+      <c r="CC14" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.6842105263157895</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.95</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>0.8260869565217391</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.88</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>518.8200000000001</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>41.5</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>519</v>
       </c>
       <c r="C15" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D15" t="n">
         <v>38</v>
-      </c>
-      <c r="D15" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E15" t="n">
         <v>519</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>509.4765937521072</v>
-      </c>
-      <c r="J15" t="n">
-        <v>46.26384714107049</v>
-      </c>
-      <c r="K15" t="n">
-        <v>521.4560146834166</v>
-      </c>
-      <c r="L15" t="n">
-        <v>41.37744492450653</v>
-      </c>
-      <c r="M15" t="n">
-        <v>528.7848975078452</v>
-      </c>
-      <c r="N15" t="n">
-        <v>38.93258587598098</v>
-      </c>
-      <c r="O15" t="n">
-        <v>521.1286694318802</v>
-      </c>
-      <c r="P15" t="n">
-        <v>45.31764355831001</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>514.8365399982206</v>
-      </c>
       <c r="R15" t="n">
-        <v>45.51155749514247</v>
+        <v>509.48</v>
       </c>
       <c r="S15" t="n">
-        <v>515.7355894263459</v>
+        <v>46.26</v>
       </c>
       <c r="T15" t="n">
-        <v>45.83484327139339</v>
+        <v>521.46</v>
       </c>
       <c r="U15" t="n">
-        <v>518.4415083638006</v>
+        <v>41.38</v>
       </c>
       <c r="V15" t="n">
-        <v>45.68079908069287</v>
+        <v>528.78</v>
       </c>
       <c r="W15" t="n">
-        <v>517.5338167101276</v>
+        <v>38.93</v>
       </c>
       <c r="X15" t="n">
-        <v>42.77635001424488</v>
+        <v>521.13</v>
       </c>
       <c r="Y15" t="n">
-        <v>513.5828686434288</v>
+        <v>45.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>41.9542522801385</v>
+        <v>514.84</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>45.51</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>515.74</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>45.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>518.4400000000001</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>45.68</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>517.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>42.78</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>513.58</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>41.95</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>505.4</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>502.9833333333333</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>501.6625</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>501.3</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>500.5666666666667</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>500.2214285714286</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>499.9125</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>499.2055555555556</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>499.095</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>68.63118824557826</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>62.43356246621061</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>58.60438203539049</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>58.28833502511459</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>56.71356882518405</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>56.33599050811668</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>54.24900776742373</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>53.43695113789315</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>50.9437530517727</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>416</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>416</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>416</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>416</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>416</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>416</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>416</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>416</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>416</v>
       </c>
-      <c r="BK15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>669</v>
-      </c>
       <c r="BT15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC15" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.8235294117647058</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.9</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.7692307692307693</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>513.58</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>41.95</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>518</v>
       </c>
       <c r="C16" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D16" t="n">
         <v>42</v>
-      </c>
-      <c r="D16" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E16" t="n">
         <v>518</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>74</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>528.0545614948913</v>
-      </c>
-      <c r="J16" t="n">
-        <v>53.77750037078713</v>
-      </c>
-      <c r="K16" t="n">
-        <v>518.0769161479311</v>
-      </c>
-      <c r="L16" t="n">
-        <v>55.35520924330604</v>
-      </c>
-      <c r="M16" t="n">
-        <v>512.1837647746324</v>
-      </c>
-      <c r="N16" t="n">
-        <v>53.98711394914283</v>
-      </c>
-      <c r="O16" t="n">
-        <v>516.7262410849025</v>
-      </c>
-      <c r="P16" t="n">
-        <v>49.74623938455613</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>517.3445236687419</v>
-      </c>
       <c r="R16" t="n">
-        <v>46.373833290756</v>
+        <v>528.05</v>
       </c>
       <c r="S16" t="n">
-        <v>512.6600954448047</v>
+        <v>53.78</v>
       </c>
       <c r="T16" t="n">
-        <v>50.72012125416206</v>
+        <v>518.08</v>
       </c>
       <c r="U16" t="n">
-        <v>508.7466724049549</v>
+        <v>55.36</v>
       </c>
       <c r="V16" t="n">
-        <v>55.85098056585601</v>
+        <v>512.1799999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>504.9678388027016</v>
+        <v>53.99</v>
       </c>
       <c r="X16" t="n">
-        <v>54.43520040052486</v>
+        <v>516.73</v>
       </c>
       <c r="Y16" t="n">
-        <v>509.059215802846</v>
+        <v>49.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>57.35291614734501</v>
+        <v>517.34</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>46.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>512.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>50.72</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>508.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>55.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>504.97</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>54.44</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>509.06</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>57.35</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>499.7</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>499</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>498.7375</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>499.68</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>500.1416666666667</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>499.6428571428572</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>499.88125</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>499.8</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>499.46</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>70.98175821998213</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>69.15224749300151</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>64.9743687445288</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>59.89772616719269</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>58.35599024283816</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>56.5477132831295</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>57.69709393407523</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>58.10167333601025</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>57.36879291043171</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>376</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>376</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>376</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>376</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>376</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>376</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>376</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>376</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>376</v>
       </c>
-      <c r="BK16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>669</v>
-      </c>
       <c r="BT16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.5</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.52</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>509.06</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>57.35</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>518</v>
       </c>
       <c r="C17" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E17" t="n">
         <v>518</v>
@@ -4542,228 +5092,261 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>532.256139048247</v>
-      </c>
-      <c r="J17" t="n">
-        <v>32.10431386552439</v>
-      </c>
-      <c r="K17" t="n">
-        <v>530.2265188533663</v>
-      </c>
-      <c r="L17" t="n">
-        <v>36.34969884524776</v>
-      </c>
-      <c r="M17" t="n">
-        <v>536.8612226696944</v>
-      </c>
-      <c r="N17" t="n">
-        <v>38.52543757476192</v>
-      </c>
-      <c r="O17" t="n">
-        <v>537.6995664928585</v>
-      </c>
-      <c r="P17" t="n">
-        <v>31.85369061819916</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>534.7025727413551</v>
-      </c>
       <c r="R17" t="n">
-        <v>34.85292902505186</v>
+        <v>532.26</v>
       </c>
       <c r="S17" t="n">
-        <v>533.2994249787977</v>
+        <v>32.1</v>
       </c>
       <c r="T17" t="n">
-        <v>37.1018484715178</v>
+        <v>530.23</v>
       </c>
       <c r="U17" t="n">
-        <v>528.1947301751867</v>
+        <v>36.35</v>
       </c>
       <c r="V17" t="n">
-        <v>39.81378644646704</v>
+        <v>536.86</v>
       </c>
       <c r="W17" t="n">
-        <v>527.8623753284335</v>
+        <v>38.53</v>
       </c>
       <c r="X17" t="n">
-        <v>39.29912542640253</v>
+        <v>537.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>524.8405772790122</v>
+        <v>31.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>41.31751032654943</v>
+        <v>534.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>34.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>533.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>37.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>528.1900000000001</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>39.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>527.86</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>39.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>524.84</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>41.32</v>
       </c>
       <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
         <v>497.175</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>497.85</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>498.5375</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>500.34</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>501.05</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>501.1785714285714</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>501.2375</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>501.4777777777778</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>501.73</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>58.66425125235981</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>57.64252625738512</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>61.28538646161905</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>60.53448934285313</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>58.12097297877936</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>57.77991097470554</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>55.59299500611566</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>55.90035336357758</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>56.04718637005786</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>357</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>357</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>357</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>357</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>357</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>357</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>357</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>357</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>357</v>
       </c>
-      <c r="BK17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>669</v>
-      </c>
       <c r="BT17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>1</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>1</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.96</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.78125</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>524.84</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>41.32</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>522</v>
       </c>
       <c r="C18" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D18" t="n">
         <v>41</v>
-      </c>
-      <c r="D18" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E18" t="n">
         <v>522</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>540.2181151294585</v>
-      </c>
-      <c r="J18" t="n">
-        <v>43.83576187756365</v>
-      </c>
-      <c r="K18" t="n">
-        <v>526.4896213639362</v>
-      </c>
-      <c r="L18" t="n">
-        <v>44.0597133828737</v>
-      </c>
-      <c r="M18" t="n">
-        <v>522.3070636992547</v>
-      </c>
-      <c r="N18" t="n">
-        <v>45.17587431368798</v>
-      </c>
-      <c r="O18" t="n">
-        <v>523.9385492518318</v>
-      </c>
-      <c r="P18" t="n">
-        <v>40.94009369198648</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>524.7516771707484</v>
-      </c>
       <c r="R18" t="n">
-        <v>43.7717083839683</v>
+        <v>540.22</v>
       </c>
       <c r="S18" t="n">
-        <v>522.7144882027926</v>
+        <v>43.84</v>
       </c>
       <c r="T18" t="n">
-        <v>54.65361898837543</v>
+        <v>526.49</v>
       </c>
       <c r="U18" t="n">
-        <v>523.7523451137167</v>
+        <v>44.06</v>
       </c>
       <c r="V18" t="n">
-        <v>58.98187481327469</v>
+        <v>522.3099999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>523.5653950897596</v>
+        <v>45.18</v>
       </c>
       <c r="X18" t="n">
-        <v>55.90297083299007</v>
+        <v>523.9400000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>521.5576013612293</v>
+        <v>40.94</v>
       </c>
       <c r="Z18" t="n">
-        <v>52.82669158713496</v>
+        <v>524.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>43.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>522.71</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>54.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>523.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>58.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>523.5700000000001</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>55.9</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>521.5599999999999</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>52.83</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>499.775</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>498.5833333333333</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>499.625</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>499.48</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>499.5583333333333</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>499.3785714285714</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>499.2375</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>499.3222222222222</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>501.315</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>82.29322192623157</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>77.54639292420735</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>70.83561515932504</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>66.70494434447869</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>62.92717958525994</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>63.00118682069669</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>71.15893193233018</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>74.89983352270147</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>74.08762227929844</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>313</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>313</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>313</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>313</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>313</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>313</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>313</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>313</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>313</v>
       </c>
-      <c r="BK18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>669</v>
-      </c>
       <c r="BT18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>0.25</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.8095238095238095</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.9642857142857143</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>521.5599999999999</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>52.83</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>520</v>
       </c>
       <c r="C19" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D19" t="n">
         <v>38</v>
-      </c>
-      <c r="D19" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E19" t="n">
         <v>520</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>504.734987758965</v>
-      </c>
-      <c r="J19" t="n">
-        <v>44.77297474562489</v>
-      </c>
-      <c r="K19" t="n">
-        <v>509.6750342506587</v>
-      </c>
-      <c r="L19" t="n">
-        <v>43.43179079512998</v>
-      </c>
-      <c r="M19" t="n">
-        <v>510.1716050232978</v>
-      </c>
-      <c r="N19" t="n">
-        <v>46.60291072012923</v>
-      </c>
-      <c r="O19" t="n">
-        <v>505.9424864410757</v>
-      </c>
-      <c r="P19" t="n">
-        <v>42.67878986138956</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>507.9489901865061</v>
-      </c>
       <c r="R19" t="n">
-        <v>43.98029665136865</v>
+        <v>504.73</v>
       </c>
       <c r="S19" t="n">
-        <v>509.5051028070756</v>
+        <v>44.77</v>
       </c>
       <c r="T19" t="n">
-        <v>42.69955470934669</v>
+        <v>509.68</v>
       </c>
       <c r="U19" t="n">
-        <v>514.8543320419345</v>
+        <v>43.43</v>
       </c>
       <c r="V19" t="n">
-        <v>41.18506097007219</v>
+        <v>510.17</v>
       </c>
       <c r="W19" t="n">
-        <v>516.1294726867163</v>
+        <v>46.6</v>
       </c>
       <c r="X19" t="n">
-        <v>43.01050109785229</v>
+        <v>505.94</v>
       </c>
       <c r="Y19" t="n">
-        <v>517.3562901865995</v>
+        <v>42.68</v>
       </c>
       <c r="Z19" t="n">
-        <v>45.62090777366359</v>
+        <v>507.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>43.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>509.51</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>42.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>514.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>41.19</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>516.13</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>43.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>517.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>45.62</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>499.4</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>499.2666666666667</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>499.1375</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>498.7</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>499.9583333333333</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>499.55</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>499.475</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>500.0222222222222</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>500.07</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>59.24559055322177</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>54.49063120288559</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>56.30491624849468</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>60.1854633611805</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>59.10659802894729</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>59.0586058806964</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>57.60500737783131</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>56.78408966872827</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>57.77322130537642</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>325</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>325</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>325</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>325</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>325</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>325</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>325</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>325</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>325</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BT19" t="n">
         <v>639</v>
       </c>
-      <c r="BL19" t="n">
+      <c r="BU19" t="n">
         <v>639</v>
       </c>
-      <c r="BM19" t="n">
+      <c r="BV19" t="n">
         <v>639</v>
       </c>
-      <c r="BN19" t="n">
+      <c r="BW19" t="n">
         <v>639</v>
       </c>
-      <c r="BO19" t="n">
+      <c r="BX19" t="n">
         <v>639</v>
       </c>
-      <c r="BP19" t="n">
+      <c r="BY19" t="n">
         <v>639</v>
       </c>
-      <c r="BQ19" t="n">
+      <c r="BZ19" t="n">
         <v>639</v>
       </c>
-      <c r="BR19" t="n">
+      <c r="CA19" t="n">
         <v>639</v>
       </c>
-      <c r="BS19" t="n">
+      <c r="CB19" t="n">
         <v>639</v>
       </c>
-      <c r="BT19" t="n">
+      <c r="CC19" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.625</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.7307692307692307</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.7307692307692307</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.8076923076923077</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.8846153846153846</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>517.36</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>45.62</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>521</v>
       </c>
       <c r="C20" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D20" t="n">
         <v>40</v>
-      </c>
-      <c r="D20" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E20" t="n">
         <v>521</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>530.8684316605182</v>
-      </c>
-      <c r="J20" t="n">
-        <v>46.32088682741291</v>
-      </c>
-      <c r="K20" t="n">
-        <v>533.6048470590719</v>
-      </c>
-      <c r="L20" t="n">
-        <v>49.90469391535359</v>
-      </c>
-      <c r="M20" t="n">
-        <v>540.2106438088813</v>
-      </c>
-      <c r="N20" t="n">
-        <v>51.31584092715971</v>
-      </c>
-      <c r="O20" t="n">
-        <v>536.38191798947</v>
-      </c>
-      <c r="P20" t="n">
-        <v>49.6187449308045</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>531.8140656580805</v>
-      </c>
       <c r="R20" t="n">
-        <v>50.26517120955324</v>
+        <v>530.87</v>
       </c>
       <c r="S20" t="n">
-        <v>529.3495289538815</v>
+        <v>46.32</v>
       </c>
       <c r="T20" t="n">
-        <v>48.24330538476666</v>
+        <v>533.6</v>
       </c>
       <c r="U20" t="n">
-        <v>531.6981308861582</v>
+        <v>49.9</v>
       </c>
       <c r="V20" t="n">
-        <v>45.68973929045816</v>
+        <v>540.21</v>
       </c>
       <c r="W20" t="n">
-        <v>523.8918835622395</v>
+        <v>51.32</v>
       </c>
       <c r="X20" t="n">
-        <v>47.83668301451458</v>
+        <v>536.38</v>
       </c>
       <c r="Y20" t="n">
-        <v>522.8101376169881</v>
+        <v>49.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>47.69232052622759</v>
+        <v>531.8099999999999</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>50.27</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>529.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>48.24</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>531.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>45.69</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>523.89</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>47.84</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>522.8099999999999</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>47.69</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>500.425</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>500.4666666666666</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>500.6375</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>502.16</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>502.4083333333334</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>502.3785714285714</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>502.43125</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>502.6055555555556</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>502.62</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>92.3747496613658</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>83.0328181437249</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>86.04115930036043</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>83.81702929596109</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>80.39822716052609</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>78.05579212123511</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>75.08849960837878</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>71.20233276626564</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>70.05216342126772</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>298</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>298</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>298</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>298</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>298</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>298</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>298</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>298</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>298</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BT20" t="n">
         <v>685</v>
       </c>
-      <c r="BL20" t="n">
+      <c r="BU20" t="n">
         <v>685</v>
       </c>
-      <c r="BM20" t="n">
+      <c r="BV20" t="n">
         <v>685</v>
       </c>
-      <c r="BN20" t="n">
+      <c r="BW20" t="n">
         <v>685</v>
       </c>
-      <c r="BO20" t="n">
+      <c r="BX20" t="n">
         <v>685</v>
       </c>
-      <c r="BP20" t="n">
+      <c r="BY20" t="n">
         <v>685</v>
       </c>
-      <c r="BQ20" t="n">
+      <c r="BZ20" t="n">
         <v>685</v>
       </c>
-      <c r="BR20" t="n">
+      <c r="CA20" t="n">
         <v>685</v>
       </c>
-      <c r="BS20" t="n">
+      <c r="CB20" t="n">
         <v>685</v>
       </c>
-      <c r="BT20" t="n">
+      <c r="CC20" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.9</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>1</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>522.8099999999999</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>47.69</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>519</v>
       </c>
       <c r="C21" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D21" t="n">
         <v>39</v>
-      </c>
-      <c r="D21" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E21" t="n">
         <v>519</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>86</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>529.7858800706308</v>
-      </c>
-      <c r="J21" t="n">
-        <v>54.21179271527957</v>
-      </c>
-      <c r="K21" t="n">
-        <v>529.2462822618269</v>
-      </c>
-      <c r="L21" t="n">
-        <v>64.41447039671142</v>
-      </c>
-      <c r="M21" t="n">
-        <v>526.9845530422466</v>
-      </c>
-      <c r="N21" t="n">
-        <v>59.44827154308599</v>
-      </c>
-      <c r="O21" t="n">
-        <v>517.5319166896068</v>
-      </c>
-      <c r="P21" t="n">
-        <v>54.27756798175348</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>522.3940126358661</v>
-      </c>
       <c r="R21" t="n">
-        <v>52.30479899372209</v>
+        <v>529.79</v>
       </c>
       <c r="S21" t="n">
-        <v>525.8703604003888</v>
+        <v>54.21</v>
       </c>
       <c r="T21" t="n">
-        <v>53.27172261046822</v>
+        <v>529.25</v>
       </c>
       <c r="U21" t="n">
-        <v>528.3606077704313</v>
+        <v>64.41</v>
       </c>
       <c r="V21" t="n">
-        <v>53.80836002857945</v>
+        <v>526.98</v>
       </c>
       <c r="W21" t="n">
-        <v>530.6996800346755</v>
+        <v>59.45</v>
       </c>
       <c r="X21" t="n">
-        <v>54.70480158008665</v>
+        <v>517.53</v>
       </c>
       <c r="Y21" t="n">
-        <v>530.2099309290628</v>
+        <v>54.28</v>
       </c>
       <c r="Z21" t="n">
-        <v>53.01732240738853</v>
+        <v>522.39</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>52.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>525.87</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>53.27</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>528.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>53.81</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>530.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>54.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>530.21</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>53.02</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>499.55</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>499.6666666666667</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>499.3</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>499.74</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>499.95</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>501.9357142857143</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>501.78125</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>501.5722222222222</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>500.055</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>105.1696130067997</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>93.81784952176686</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>85.08104959390194</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>80.88839471766022</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>82.08906240582034</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>82.07211208219667</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>85.67844477135132</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>89.38394278837258</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>88.42890915871348</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>320</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>320</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>320</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>320</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>320</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>320</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>320</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>320</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>320</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>706</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>706</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>706</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>706</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>706</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>706</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>706</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>706</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>706</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>1</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>530.21</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>53.02</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>520.15</v>
       </c>
       <c r="C22" t="n">
+        <v>58.93254262416605</v>
+      </c>
+      <c r="D22" t="n">
         <v>39.75</v>
-      </c>
-      <c r="D22" t="n">
-        <v>58.93254262416605</v>
       </c>
       <c r="E22" t="n">
         <v>520.15</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>78.05</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.628</v>
+      </c>
       <c r="I22" t="n">
-        <v>521.4530443580932</v>
+        <v>2.6815</v>
       </c>
       <c r="J22" t="n">
-        <v>45.9669600068725</v>
+        <v>2.699</v>
       </c>
       <c r="K22" t="n">
-        <v>520.3482325246181</v>
+        <v>2.739</v>
       </c>
       <c r="L22" t="n">
-        <v>46.68106670638273</v>
+        <v>2.772</v>
       </c>
       <c r="M22" t="n">
-        <v>520.6519555094605</v>
+        <v>2.807</v>
       </c>
       <c r="N22" t="n">
-        <v>47.86139654910026</v>
+        <v>2.384</v>
       </c>
       <c r="O22" t="n">
-        <v>520.9352540351208</v>
+        <v>2.395</v>
       </c>
       <c r="P22" t="n">
-        <v>46.07734156940505</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>520.5783826735743</v>
-      </c>
+        <v>2.522</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>46.41677342386504</v>
+        <v>521.452</v>
       </c>
       <c r="S22" t="n">
-        <v>519.7378865789254</v>
+        <v>45.96650000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>47.61089612720241</v>
+        <v>520.3485000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>520.1210730209356</v>
+        <v>46.681</v>
       </c>
       <c r="V22" t="n">
-        <v>47.57212838266021</v>
+        <v>520.6510000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>519.8796874644797</v>
+        <v>47.86200000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>46.89174109443861</v>
+        <v>520.9350000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>519.7851360863024</v>
+        <v>46.0775</v>
       </c>
       <c r="Z22" t="n">
-        <v>47.04530728581999</v>
+        <v>520.579</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>46.41549999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>519.7380000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>47.6095</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>520.1195</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>47.57250000000001</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>519.8794999999999</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>46.8915</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>519.7855</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>47.0455</v>
       </c>
       <c r="AJ22" t="n">
-        <v>499.2299999999999</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>499.2683333333333</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>498.9775000000001</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>499.23</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>499.268</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>498.9789999999999</v>
+      </c>
+      <c r="AV22" t="n">
         <v>499.3385</v>
       </c>
-      <c r="AN22" t="n">
-        <v>499.645</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>499.6582142857142</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>499.51875</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>499.4130555555556</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>499.28675</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>71.42675893592148</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>66.34034547311531</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>65.11329717221506</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>64.02774108826972</v>
-      </c>
       <c r="AW22" t="n">
-        <v>62.84913095765945</v>
+        <v>499.6455</v>
       </c>
       <c r="AX22" t="n">
-        <v>62.51247925573877</v>
+        <v>499.6579999999999</v>
       </c>
       <c r="AY22" t="n">
-        <v>62.79139631292386</v>
+        <v>499.5195000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>62.52246774134538</v>
+        <v>499.413</v>
       </c>
       <c r="BA22" t="n">
-        <v>61.83436484407459</v>
+        <v>499.2875</v>
       </c>
       <c r="BB22" t="n">
+        <v>71.426</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>66.3395</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>65.11299999999999</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>64.02700000000002</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>62.8495</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>62.51299999999999</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>62.79199999999999</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>62.52200000000001</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>61.834</v>
+      </c>
+      <c r="BK22" t="n">
         <v>351.7</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>351.7</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>351.65</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>351.65</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>351.65</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>351.65</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>351.65</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>351.65</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>351.65</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>658.7</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>658.7</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>658.7</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>658.7</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>658.7</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>658.7</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>658.7</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>658.7</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>658.7</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6443976856476856</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.690936124157621</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7034260025320397</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.7961273158746444</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.8267870114463918</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.8170064748105089</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.8473243471462168</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8381795653572672</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.8296073268531809</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>519.7855</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>47.0455</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.348488432516786</v>
       </c>
       <c r="C23" t="n">
+        <v>2.300577111748359</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.55173926187427</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.300577111748359</v>
       </c>
       <c r="E23" t="n">
         <v>1.348488432516786</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03654845377966365</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>2.316417378989419</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.290437057226736</v>
+      </c>
       <c r="I23" t="n">
-        <v>13.93378791587302</v>
+        <v>0.2791203287020436</v>
       </c>
       <c r="J23" t="n">
-        <v>8.740666529553913</v>
+        <v>0.2728774546626341</v>
       </c>
       <c r="K23" t="n">
-        <v>11.15130287178304</v>
+        <v>0.2297114895277392</v>
       </c>
       <c r="L23" t="n">
-        <v>7.492975771975572</v>
+        <v>0.177900031064167</v>
       </c>
       <c r="M23" t="n">
-        <v>10.19156777075715</v>
+        <v>0.139325442570151</v>
       </c>
       <c r="N23" t="n">
-        <v>7.323573597881123</v>
+        <v>0.2326596791792456</v>
       </c>
       <c r="O23" t="n">
-        <v>9.208207990037351</v>
+        <v>0.2670994295448005</v>
       </c>
       <c r="P23" t="n">
-        <v>8.212313037377484</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9.275430881937806</v>
-      </c>
+        <v>0.2790132990605136</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>6.604367270772566</v>
+        <v>13.93451738442498</v>
       </c>
       <c r="S23" t="n">
-        <v>8.811885436802624</v>
+        <v>8.74065713234784</v>
       </c>
       <c r="T23" t="n">
-        <v>6.718940691892145</v>
+        <v>11.15118793530183</v>
       </c>
       <c r="U23" t="n">
-        <v>8.97083544597792</v>
+        <v>7.49254780642599</v>
       </c>
       <c r="V23" t="n">
-        <v>6.701067129840055</v>
+        <v>10.19114729350405</v>
       </c>
       <c r="W23" t="n">
-        <v>9.115235250896895</v>
+        <v>7.323368940015172</v>
       </c>
       <c r="X23" t="n">
-        <v>5.990816980918427</v>
+        <v>9.208187146573197</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.557051976979013</v>
+        <v>8.213054355238693</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.539634820352402</v>
+        <v>9.274731319700402</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>6.604037421392908</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>8.811794488369729</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>6.718418105633591</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>8.970957512117113</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>6.700962911952909</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>9.116750041313486</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>5.991235945770684</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>8.557018341381349</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.539808542198054</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.884436458688338</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.978236115496556</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.738101467270057</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.884488461445204</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.978666749420724</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.736793476193235</v>
+      </c>
+      <c r="AV23" t="n">
         <v>2.057559297604306</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.649320700145931</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1.804267936678317</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.640747332531893</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.686464552491287</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.760657230007862</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>12.16990390092058</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>9.950957593400767</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>9.104760364938782</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.469419819580855</v>
-      </c>
       <c r="AW23" t="n">
-        <v>8.681133022925376</v>
+        <v>1.648930993417441</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.530141544794724</v>
+        <v>1.804927757702872</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.033686855442269</v>
+        <v>1.639597110332451</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9.579300434674742</v>
+        <v>1.686850381784446</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.489574921425042</v>
+        <v>1.760531842489951</v>
       </c>
       <c r="BB23" t="n">
+        <v>12.16905410846451</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>9.951487841682663</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>9.105373254582329</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.469766906484969</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>8.681020722787943</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>8.529928795901986</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>9.033386379076466</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>9.578244317750844</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9.490308297360386</v>
+      </c>
+      <c r="BK23" t="n">
         <v>29.61702924083764</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>29.61702924083764</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>29.54260972686205</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>29.54260972686205</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>29.54260972686205</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>29.54260972686205</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>29.54260972686205</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>29.54260972686205</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>29.54260972686205</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>29.28642581200555</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>29.28642581200555</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>29.28642581200555</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>29.28642581200555</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>29.28642581200555</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>29.28642581200555</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>29.28642581200555</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>29.28642581200555</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>29.28642581200555</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2335365279365659</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2298251455701278</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2540373402777003</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.1302980903840391</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.1150208321200094</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.1174156136462931</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.110200251716559</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.1022794645176912</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.1374980891377119</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>8.557018341381349</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>5.539808542198054</v>
       </c>
     </row>
   </sheetData>
